--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261016.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20261016.xlsx
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠東銀</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>104,971,502</t>
+          <t>13,112,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>遠東銀</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>13,112,000</t>
+          <t>104,971,502</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>3,513,000</t>
+          <t>2,360,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,360,000</t>
+          <t>3,513,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>56,668,000</t>
+          <t>16,273,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>16,273,000</t>
+          <t>56,668,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
